--- a/sheets/민요/검수/베틀가.xlsx
+++ b/sheets/민요/검수/베틀가.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,36 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1475,8 +1585,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:M14"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -1491,488 +1605,391 @@
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">베틀가 — 민요채보-1/베틀가.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">베틀가</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">베</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">옥</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">베</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="13"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="15"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="13"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="16"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">심</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">틀</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="K6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">난</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">틀</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="13"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="15"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="13"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="16"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="J9" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="K9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="13"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="15"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="13"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="16"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">湳</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="J12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="K12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="L12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">놓</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="13"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="15"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="13"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="16"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:M2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="100"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/베틀가.xlsx
+++ b/sheets/민요/검수/베틀가.xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -744,12 +744,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -928,12 +928,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|湳</t>
+          <t xml:space="preserve">–|湳</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 湳</t>
         </is>
       </c>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|潢</t>
+          <t xml:space="preserve">–|潢</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|姑</t>
+          <t xml:space="preserve">–|姑</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
@@ -1720,12 +1720,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|湳</t>
+          <t xml:space="preserve">–|湳</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 湳</t>
         </is>
       </c>
@@ -2108,12 +2108,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -2148,12 +2148,12 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|姑</t>
+          <t xml:space="preserve">–|姑</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
@@ -2478,7 +2478,7 @@
       <c r="E5" s="16"/>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
@@ -2572,7 +2572,7 @@
       <c r="A8" s="0"/>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -2589,14 +2589,14 @@
       <c r="E8" s="10"/>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
       <c r="G8" s="10"/>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -2606,7 +2606,7 @@
       <c r="A9" s="0"/>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
@@ -2649,7 +2649,7 @@
       <c r="C10" s="9"/>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 湳</t>
         </is>
       </c>
@@ -2752,7 +2752,7 @@
       <c r="G13" s="9"/>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 湳</t>
         </is>
       </c>
@@ -2774,7 +2774,7 @@
       <c r="E14" s="13"/>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 姑</t>
         </is>
       </c>

--- a/sheets/민요/검수/베틀가.xlsx
+++ b/sheets/민요/검수/베틀가.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,39 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2366,53 +2413,53 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">베틀가</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C3" s="22"/>
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">애</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="G3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">옥</t>
         </is>
       </c>
-      <c r="H3" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="H3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">베</t>
         </is>
@@ -2420,38 +2467,38 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E4" s="12"/>
-      <c r="F4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="E4" s="26"/>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">난</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">틀</t>
         </is>
@@ -2459,36 +2506,36 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="E5" s="16"/>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="29"/>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="G5" s="27"/>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
@@ -2496,296 +2543,296 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">배</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">천</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I6" s="8"/>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I6" s="22"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">틀</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="E7" s="26"/>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I7" s="9"/>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I7" s="25"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E8" s="27"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="G8" s="27"/>
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I8" s="10"/>
+      <c r="I8" s="27"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">삽</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I9" s="11"/>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G9" s="22"/>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I9" s="24"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="25"/>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 湳</t>
         </is>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E10" s="25"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I10" s="9"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I10" s="25"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C11" s="27"/>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="E11" s="30"/>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="G11" s="27"/>
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I11" s="10"/>
+      <c r="I11" s="27"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="C12" s="22"/>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="18" t="inlineStr">
+      <c r="G12" s="22"/>
+      <c r="H12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I12" s="11"/>
+      <c r="I12" s="24"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="C13" s="25"/>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="G13" s="25"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 湳</t>
         </is>
       </c>
-      <c r="I13" s="9"/>
+      <c r="I13" s="25"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="C14" s="27"/>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="E14" s="30"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="G14" s="27"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
+      <c r="I14" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/베틀가.xlsx
+++ b/sheets/민요/검수/베틀가.xlsx
@@ -2398,20 +2398,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="D4" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E4" s="26"/>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="I6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="D7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E7" s="26"/>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="I7" s="25"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="I8" s="27"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="I9" s="24"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="I10" s="25"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="I11" s="27"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="I12" s="24"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -2805,11 +2805,11 @@
       </c>
       <c r="I13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C14" s="27"/>

--- a/sheets/민요/검수/베틀가.xlsx
+++ b/sheets/민요/검수/베틀가.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -240,6 +245,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2433,13 +2459,13 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C3" s="22"/>
+      <c r="C3" s="31"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">애</t>
         </is>
@@ -2449,7 +2475,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G3" s="24" t="inlineStr">
+      <c r="G3" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">옥</t>
         </is>
@@ -2459,7 +2485,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I3" s="24" t="inlineStr">
+      <c r="I3" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">베</t>
         </is>
@@ -2472,7 +2498,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -2482,13 +2508,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E4" s="26"/>
+      <c r="E4" s="34"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G4" s="25" t="inlineStr">
+      <c r="G4" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">난</t>
         </is>
@@ -2498,7 +2524,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I4" s="25" t="inlineStr">
+      <c r="I4" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">틀</t>
         </is>
@@ -2512,7 +2538,7 @@
 無</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
@@ -2522,20 +2548,20 @@
           <t xml:space="preserve">?</t>
         </is>
       </c>
-      <c r="E5" s="29"/>
+      <c r="E5" s="36"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 潢</t>
         </is>
       </c>
-      <c r="G5" s="27"/>
+      <c r="G5" s="35"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I5" s="27" t="inlineStr">
+      <c r="I5" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
@@ -2548,7 +2574,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">배</t>
         </is>
@@ -2558,7 +2584,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
@@ -2568,7 +2594,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">천</t>
         </is>
@@ -2578,7 +2604,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I6" s="22"/>
+      <c r="I6" s="31"/>
     </row>
     <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
@@ -2587,7 +2613,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">틀</t>
         </is>
@@ -2597,13 +2623,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E7" s="26"/>
+      <c r="E7" s="34"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G7" s="25" t="inlineStr">
+      <c r="G7" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -2613,7 +2639,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I7" s="25"/>
+      <c r="I7" s="33"/>
     </row>
     <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
@@ -2623,7 +2649,7 @@
 無</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="35" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -2633,21 +2659,21 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E8" s="27"/>
+      <c r="E8" s="35"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="G8" s="27"/>
+      <c r="G8" s="35"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I8" s="27"/>
+      <c r="I8" s="35"/>
     </row>
     <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
@@ -2657,7 +2683,7 @@
 姑</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
@@ -2667,7 +2693,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="E9" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">삽</t>
         </is>
@@ -2677,13 +2703,13 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G9" s="22"/>
+      <c r="G9" s="31"/>
       <c r="H9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I9" s="24"/>
+      <c r="I9" s="32"/>
     </row>
     <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
@@ -2693,26 +2719,26 @@
 姑</t>
         </is>
       </c>
-      <c r="C10" s="25"/>
+      <c r="C10" s="33"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 湳</t>
         </is>
       </c>
-      <c r="E10" s="25"/>
+      <c r="E10" s="33"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G10" s="25"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I10" s="25"/>
+      <c r="I10" s="33"/>
     </row>
     <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
@@ -2721,25 +2747,25 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C11" s="27"/>
+      <c r="C11" s="35"/>
       <c r="D11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E11" s="30"/>
+      <c r="E11" s="37"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G11" s="27"/>
+      <c r="G11" s="35"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I11" s="27"/>
+      <c r="I11" s="35"/>
     </row>
     <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
@@ -2749,13 +2775,13 @@
 姑</t>
         </is>
       </c>
-      <c r="C12" s="22"/>
+      <c r="C12" s="31"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -2765,13 +2791,13 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G12" s="22"/>
+      <c r="G12" s="31"/>
       <c r="H12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I12" s="24"/>
+      <c r="I12" s="32"/>
     </row>
     <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
@@ -2780,13 +2806,13 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C13" s="25"/>
+      <c r="C13" s="33"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -2796,14 +2822,14 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G13" s="25"/>
+      <c r="G13" s="33"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 湳</t>
         </is>
       </c>
-      <c r="I13" s="25"/>
+      <c r="I13" s="33"/>
     </row>
     <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
@@ -2812,27 +2838,27 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C14" s="27"/>
+      <c r="C14" s="35"/>
       <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E14" s="30"/>
+      <c r="E14" s="37"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
-      <c r="G14" s="27"/>
+      <c r="G14" s="35"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="I14" s="27"/>
+      <c r="I14" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/베틀가.xlsx
+++ b/sheets/민요/검수/베틀가.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -223,49 +218,22 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -374,7 +342,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
     </row>
@@ -386,7 +354,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -398,7 +366,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">중</t>
+          <t xml:space="preserve">상</t>
         </is>
       </c>
     </row>
@@ -410,7 +378,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">팔레트 외 글자 1, 비고 23%</t>
+          <t xml:space="preserve">한 장에 두 곡</t>
         </is>
       </c>
     </row>
@@ -438,7 +406,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">손으로 그린 격자, 번호 없음. 12정간·굵은 선 3칸마다 → 굿거리 3/4. 중앙 세로 라벨 "(베틀가)(굿거리)". 오른쪽 절반은 크게 X로 지운 별도 곡 "〈뱃놀이〉〈중모리〉"(나무아미타불 등 가사)라서 제외함. 베틀가 본곡은 왼쪽 4줄만 판독. 4줄 1정간 왼쪽 칸에 지운 낙서(배?) 있음. 삼수변+仲=㳞, 삼수변 글자 다수. AI 재판독 초안.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자, 번호 없음. 12정간·굵은 선 3칸마다 → 3/4. 중앙 세로 라벨 "(베틀가)(굿거리)", 위에 "정악식" 메모. 한 장에 두 곡: 오른쪽 4줄은 X로 지운 다른 곡 〈뱃놀이〉〈중모리〉(나무아미타불 등)라 제외, 베틀가 왼쪽 4줄만 판독. 줄1·2는 7정간부터 같은 가사 반복(베틀을 놓세). 4줄 4정간 율명은 지우고 격자 왼쪽 밖에 고쳐 씀.</t>
         </is>
       </c>
     </row>
@@ -624,26 +592,22 @@
       <c r="F2" s="2">
         <v>1</v>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">베</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">삼수변+仲</t>
-        </is>
-      </c>
+      <c r="J2" s="4"/>
       <c r="K2" s="2"/>
     </row>
     <row r="3">
@@ -708,12 +672,13 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">–|㴌</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">–
+㴌</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -755,7 +720,11 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I5" s="2"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">놓</t>
+        </is>
+      </c>
       <c r="J5" s="4"/>
       <c r="K5" s="2"/>
     </row>
@@ -790,7 +759,11 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I6" s="2"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세</t>
+        </is>
+      </c>
       <c r="J6" s="4"/>
       <c r="K6" s="2"/>
     </row>
@@ -851,22 +824,22 @@
       <c r="F8" s="2">
         <v>3</v>
       </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I8" s="3"/>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵계열, 흐림</t>
-        </is>
-      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">베</t>
+        </is>
+      </c>
+      <c r="J8" s="4"/>
       <c r="K8" s="2"/>
     </row>
     <row r="9">
@@ -892,15 +865,20 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞|湳</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I9" s="2"/>
+          <t xml:space="preserve">㳞
+湳</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">틀</t>
+        </is>
+      </c>
       <c r="J9" s="4"/>
       <c r="K9" s="2"/>
     </row>
@@ -927,15 +905,20 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I10" s="2"/>
+          <t xml:space="preserve">㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">을</t>
+        </is>
+      </c>
       <c r="J10" s="4"/>
       <c r="K10" s="2"/>
     </row>
@@ -960,22 +943,22 @@
       <c r="F11" s="2">
         <v>4</v>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I11" s="3"/>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">氵無/仲? 확실치 않음</t>
-        </is>
-      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">놓</t>
+        </is>
+      </c>
+      <c r="J11" s="4"/>
       <c r="K11" s="2"/>
     </row>
     <row r="12">
@@ -1001,16 +984,20 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|湳</t>
+          <t xml:space="preserve">–|㴌</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-湳</t>
-        </is>
-      </c>
-      <c r="I12" s="2"/>
+㴌</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세</t>
+        </is>
+      </c>
       <c r="J12" s="4"/>
       <c r="K12" s="2"/>
     </row>
@@ -1035,19 +1022,23 @@
       <c r="F13" s="2">
         <v>4</v>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢|姑</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="4"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아래 글자 姑/㴌?</t>
+        </is>
+      </c>
       <c r="K13" s="2"/>
     </row>
     <row r="14">
@@ -1071,26 +1062,22 @@
       <c r="F14" s="2">
         <v>1</v>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">옥</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">삼수변+仲</t>
-        </is>
-      </c>
+      <c r="J14" s="4"/>
       <c r="K14" s="2"/>
     </row>
     <row r="15">
@@ -1155,13 +1142,13 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|潢</t>
+          <t xml:space="preserve">–|㴌</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="I16" s="2"/>
@@ -1201,7 +1188,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">천</t>
+          <t xml:space="preserve">간</t>
         </is>
       </c>
       <c r="J17" s="4"/>
@@ -1278,7 +1265,11 @@
 無</t>
         </is>
       </c>
-      <c r="I19" s="2"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
       <c r="J19" s="4"/>
       <c r="K19" s="2"/>
     </row>
@@ -1305,15 +1296,19 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I20" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">베</t>
+        </is>
+      </c>
       <c r="J20" s="4"/>
       <c r="K20" s="2"/>
     </row>
@@ -1340,15 +1335,20 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">無|姑</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I21" s="2"/>
+          <t xml:space="preserve">無
+姑</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">틀</t>
+        </is>
+      </c>
       <c r="J21" s="4"/>
       <c r="K21" s="2"/>
     </row>
@@ -1375,15 +1375,19 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I22" s="2"/>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">을</t>
+        </is>
+      </c>
       <c r="J22" s="4"/>
       <c r="K22" s="2"/>
     </row>
@@ -1410,15 +1414,20 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">無|姑</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I23" s="2"/>
+          <t xml:space="preserve">無
+姑</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">놓</t>
+        </is>
+      </c>
       <c r="J23" s="4"/>
       <c r="K23" s="2"/>
     </row>
@@ -1453,7 +1462,11 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I24" s="2"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세</t>
+        </is>
+      </c>
       <c r="J24" s="4"/>
       <c r="K24" s="2"/>
     </row>
@@ -1480,13 +1493,13 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|姑</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-姑</t>
+△</t>
         </is>
       </c>
       <c r="I25" s="2"/>
@@ -1526,7 +1539,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">애</t>
+          <t xml:space="preserve">에</t>
         </is>
       </c>
       <c r="J26" s="4"/>
@@ -1553,22 +1566,18 @@
       <c r="F27" s="2">
         <v>1</v>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I27" s="3"/>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작은 점</t>
-        </is>
-      </c>
+      <c r="I27" s="2"/>
+      <c r="J27" s="4"/>
       <c r="K27" s="2"/>
     </row>
     <row r="28">
@@ -1592,27 +1601,23 @@
       <c r="F28" s="2">
         <v>1</v>
       </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
-      <c r="I28" s="5"/>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">尙/南 비슷, 못 읽음</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해</t>
+        </is>
+      </c>
+      <c r="J28" s="4"/>
+      <c r="K28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" s="2">
@@ -1674,22 +1679,18 @@
       <c r="F30" s="2">
         <v>2</v>
       </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I30" s="3"/>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작은 두 점</t>
-        </is>
-      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">··</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">··</t>
+        </is>
+      </c>
+      <c r="I30" s="2"/>
+      <c r="J30" s="4"/>
       <c r="K30" s="2"/>
     </row>
     <row r="31">
@@ -1723,7 +1724,11 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I31" s="2"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오</t>
+        </is>
+      </c>
       <c r="J31" s="4"/>
       <c r="K31" s="2"/>
     </row>
@@ -1748,26 +1753,22 @@
       <c r="F32" s="2">
         <v>3</v>
       </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">삽</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">삼수변? 확실치 않음</t>
-        </is>
-      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">베</t>
+        </is>
+      </c>
+      <c r="J32" s="4"/>
       <c r="K32" s="2"/>
     </row>
     <row r="33">
@@ -1791,58 +1792,66 @@
       <c r="F33" s="2">
         <v>3</v>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">짜</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 짜/쫘?</t>
+        </is>
+      </c>
+      <c r="K33" s="2"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2">
+        <v>1</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/베틀가.png</t>
+        </is>
+      </c>
+      <c r="C34" s="2">
+        <v>3</v>
+      </c>
+      <c r="D34" s="2">
+        <v>3</v>
+      </c>
+      <c r="E34" s="2">
+        <v>9</v>
+      </c>
+      <c r="F34" s="2">
+        <v>3</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–|湳</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 湳</t>
         </is>
       </c>
-      <c r="I33" s="2"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="2"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2">
-        <v>1</v>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/베틀가.png</t>
-        </is>
-      </c>
-      <c r="C34" s="2">
-        <v>3</v>
-      </c>
-      <c r="D34" s="2">
-        <v>3</v>
-      </c>
-      <c r="E34" s="2">
-        <v>9</v>
-      </c>
-      <c r="F34" s="2">
-        <v>3</v>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I34" s="3"/>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">삼수변+仲</t>
-        </is>
-      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">는</t>
+        </is>
+      </c>
+      <c r="J34" s="4"/>
       <c r="K34" s="2"/>
     </row>
     <row r="35">
@@ -1868,12 +1877,13 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㳞
+㴌</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -1944,22 +1954,23 @@
       <c r="F37" s="2">
         <v>4</v>
       </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I37" s="3"/>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">삼수변+仲</t>
-        </is>
-      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌|△</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+△</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">씨</t>
+        </is>
+      </c>
+      <c r="J37" s="4"/>
       <c r="K37" s="2"/>
     </row>
     <row r="38">
@@ -1993,7 +2004,11 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I38" s="2"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사</t>
+        </is>
+      </c>
       <c r="J38" s="4"/>
       <c r="K38" s="2"/>
     </row>
@@ -2030,7 +2045,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">사</t>
+          <t xml:space="preserve">랑</t>
         </is>
       </c>
       <c r="J39" s="4"/>
@@ -2070,7 +2085,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">랑</t>
+          <t xml:space="preserve">노래</t>
         </is>
       </c>
       <c r="J40" s="4"/>
@@ -2099,22 +2114,22 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">배</t>
+          <t xml:space="preserve">베</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">왼쪽 지운 낙서 있음</t>
+          <t xml:space="preserve">칸 율명을 지우고 왼쪽 밖에 고쳐 씀(潢?)</t>
         </is>
       </c>
       <c r="K41" s="2"/>
@@ -2219,23 +2234,26 @@
       <c r="F44" s="2">
         <v>3</v>
       </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|姑</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-姑</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
       </c>
-      <c r="J44" s="4"/>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">古 모양, 南으로 판독</t>
+        </is>
+      </c>
       <c r="K44" s="2"/>
     </row>
     <row r="45">
@@ -2259,19 +2277,27 @@
       <c r="F45" s="2">
         <v>3</v>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">無|姑</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="I45" s="2"/>
-      <c r="J45" s="4"/>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">심</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 심 뒤 먹칠</t>
+        </is>
+      </c>
       <c r="K45" s="2"/>
     </row>
     <row r="46">
@@ -2305,7 +2331,11 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I46" s="2"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">만</t>
+        </is>
+      </c>
       <c r="J46" s="4"/>
       <c r="K46" s="2"/>
     </row>
@@ -2341,7 +2371,11 @@
 姑</t>
         </is>
       </c>
-      <c r="I47" s="2"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가누</t>
+        </is>
+      </c>
       <c r="J47" s="4"/>
       <c r="K47" s="2"/>
     </row>
@@ -2376,7 +2410,11 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I48" s="2"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나</t>
+        </is>
+      </c>
       <c r="J48" s="4"/>
       <c r="K48" s="2"/>
     </row>
@@ -2403,12 +2441,13 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I49" s="2"/>
@@ -2437,7 +2476,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="55.19" customHeight="1">
+    <row r="2" ht="52.21" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2452,69 +2491,73 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="55.19" customHeight="1">
+    <row r="3" ht="52.21" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C3" s="31"/>
+      <c r="C3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사</t>
+        </is>
+      </c>
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E3" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">애</t>
-        </is>
-      </c>
-      <c r="F3" s="23" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G3" s="32" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">옥</t>
         </is>
       </c>
-      <c r="H3" s="23" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I3" s="32" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">베</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="55.19" customHeight="1">
+    <row r="4" ht="52.21" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C4" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사</t>
-        </is>
-      </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">랑</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E4" s="34"/>
+      <c r="E4" s="23"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G4" s="33" t="inlineStr">
+      <c r="G4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">난</t>
         </is>
@@ -2524,13 +2567,13 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I4" s="33" t="inlineStr">
+      <c r="I4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">틀</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="55.19" customHeight="1">
+    <row r="5" ht="52.21" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2538,98 +2581,108 @@
 無</t>
         </is>
       </c>
-      <c r="C5" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">랑</t>
-        </is>
-      </c>
-      <c r="D5" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
-      <c r="E5" s="36"/>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">노
+래</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해</t>
+        </is>
+      </c>
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-潢</t>
-        </is>
-      </c>
-      <c r="G5" s="35"/>
+㴌</t>
+        </is>
+      </c>
+      <c r="G5" s="24"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">–
+㴌</t>
+        </is>
+      </c>
+      <c r="I5" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">을</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="52.21" customHeight="1">
+      <c r="A6" s="0"/>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">베</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">간</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I5" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">을</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="55.19" customHeight="1">
-      <c r="A6" s="0"/>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="C6" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">배</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="E6" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">오</t>
-        </is>
-      </c>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G6" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">천</t>
-        </is>
-      </c>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I6" s="31"/>
-    </row>
-    <row r="7" ht="55.19" customHeight="1">
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">놓</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52.21" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C7" s="33" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">틀</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E7" s="34"/>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">––</t>
+        </is>
+      </c>
+      <c r="E7" s="23"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G7" s="33" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -2639,9 +2692,13 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I7" s="33"/>
-    </row>
-    <row r="8" ht="55.19" customHeight="1">
+      <c r="I7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="52.21" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2649,7 +2706,7 @@
 無</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -2659,115 +2716,165 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E8" s="35"/>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오</t>
+        </is>
+      </c>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="G8" s="35"/>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I8" s="35"/>
-    </row>
-    <row r="9" ht="55.19" customHeight="1">
+      <c r="I8" s="24"/>
+    </row>
+    <row r="9" ht="52.21" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-姑</t>
-        </is>
-      </c>
-      <c r="C9" s="31" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E9" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">삽</t>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">베</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G9" s="31"/>
-      <c r="H9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I9" s="32"/>
-    </row>
-    <row r="10" ht="55.19" customHeight="1">
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">베</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">베</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52.21" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">심</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="E10" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">짜</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+姑</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">틀</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+湳</t>
+        </is>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">틀</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="52.21" customHeight="1">
+      <c r="A11" s="0"/>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">만</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 湳</t>
         </is>
       </c>
-      <c r="E10" s="33"/>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G10" s="33"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I10" s="33"/>
-    </row>
-    <row r="11" ht="55.19" customHeight="1">
-      <c r="A11" s="0"/>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">는</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C11" s="35"/>
-      <c r="D11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="E11" s="37"/>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G11" s="35"/>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">을</t>
+        </is>
+      </c>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I11" s="35"/>
-    </row>
-    <row r="12" ht="55.19" customHeight="1">
+          <t xml:space="preserve">㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">을</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52.21" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -2775,44 +2882,63 @@
 姑</t>
         </is>
       </c>
-      <c r="C12" s="31"/>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가
+누</t>
+        </is>
+      </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E12" s="31" t="inlineStr">
+          <t xml:space="preserve">㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G12" s="31"/>
-      <c r="H12" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I12" s="32"/>
-    </row>
-    <row r="13" ht="55.19" customHeight="1">
+          <t xml:space="preserve">無
+姑</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">놓</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">놓</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="52.21" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C13" s="33"/>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나</t>
+        </is>
+      </c>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E13" s="33" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -2822,43 +2948,57 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G13" s="33"/>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세</t>
+        </is>
+      </c>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-湳</t>
-        </is>
-      </c>
-      <c r="I13" s="33"/>
-    </row>
-    <row r="14" ht="55.19" customHeight="1">
+㴌</t>
+        </is>
+      </c>
+      <c r="I13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52.21" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="E14" s="37"/>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="C14" s="24"/>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+△</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">씨</t>
+        </is>
+      </c>
       <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-姑</t>
-        </is>
-      </c>
-      <c r="G14" s="35"/>
-      <c r="H14" s="21" t="inlineStr">
+△</t>
+        </is>
+      </c>
+      <c r="G14" s="24"/>
+      <c r="H14" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="I14" s="35"/>
+      <c r="I14" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/베틀가.xlsx
+++ b/sheets/민요/검수/베틀가.xlsx
@@ -461,10 +461,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/베틀가.xlsx
+++ b/sheets/민요/검수/베틀가.xlsx
@@ -362,24 +362,8 @@
     <t xml:space="preserve">––</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
+    <t xml:space="preserve">無
+南</t>
   </si>
   <si>
     <t xml:space="preserve">가
@@ -402,17 +386,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -534,7 +518,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="28">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -596,6 +580,54 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2544,332 +2576,332 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:I14"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="17" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="17" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="17" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="17" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="43.01" customHeight="true">
+      <c r="B2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B3" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="20" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B4" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="7" t="s">
+      <c r="E4" s="21"/>
+      <c r="F4" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="21" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B5" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="7" t="s">
+      <c r="G5" s="22"/>
+      <c r="H5" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="22" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="11" t="s">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B6" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="20" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B7" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="7" t="s">
+      <c r="E7" s="21"/>
+      <c r="F7" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="21" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B8" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="I8" s="10"/>
-    </row>
-    <row r="9" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="13" t="s">
+      <c r="I8" s="22"/>
+    </row>
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B9" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="20" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="13" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B10" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="I10" s="21" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B11" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="22" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B12" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="20" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B13" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="I13" s="21" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7" t="s">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.87" customHeight="true">
+      <c r="B14" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="7" t="s">
+      <c r="C14" s="22"/>
+      <c r="D14" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="13" t="s">
+      <c r="G14" s="22"/>
+      <c r="H14" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="I14" s="15"/>
+      <c r="I14" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2877,7 +2909,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="93"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/베틀가.xlsx
+++ b/sheets/민요/검수/베틀가.xlsx
@@ -2582,13 +2582,13 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="16" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="17" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="16" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="17" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="16" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="17" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="16" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="17" width="6"/>
   </cols>
   <sheetData>
